--- a/data/trans_bre/IP2005-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 4,96</t>
+          <t>-8,96; 5,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 1,34</t>
+          <t>-5,07; 1,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 0,0</t>
+          <t>-2,72; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 6,76</t>
+          <t>-16,92; 6,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 5,55</t>
+          <t>-9,61; 5,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 1,36</t>
+          <t>-5,08; 1,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 0,0</t>
+          <t>-2,72; 0,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 8,75</t>
+          <t>-19,19; 8,38</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 4,57</t>
+          <t>-2,86; 4,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 2,54</t>
+          <t>-5,45; 2,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 2,04</t>
+          <t>-4,8; 2,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 4,86</t>
+          <t>-6,54; 5,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 5,11</t>
+          <t>-3,13; 4,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 2,76</t>
+          <t>-5,73; 2,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 2,16</t>
+          <t>-4,98; 2,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 5,7</t>
+          <t>-7,21; 5,95</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 5,57</t>
+          <t>-8,75; 5,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 6,72</t>
+          <t>-5,12; 7,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 12,9</t>
+          <t>2,13; 12,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 7,72</t>
+          <t>-4,41; 8,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 6,76</t>
+          <t>-9,86; 7,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 8,19</t>
+          <t>-5,76; 8,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 16,2</t>
+          <t>2,5; 16,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 9,29</t>
+          <t>-4,97; 10,16</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 6,43</t>
+          <t>-5,03; 5,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 6,62</t>
+          <t>-4,78; 7,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 8,46</t>
+          <t>-3,13; 8,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 5,09</t>
+          <t>-5,21; 5,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 7,73</t>
+          <t>-5,69; 6,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 7,91</t>
+          <t>-5,39; 8,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 10,24</t>
+          <t>-3,39; 10,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 5,83</t>
+          <t>-5,65; 6,0</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 2,81</t>
+          <t>-2,93; 2,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 1,82</t>
+          <t>-3,19; 2,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 4,45</t>
+          <t>-0,29; 4,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,84</t>
+          <t>-3,25; 3,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 3,21</t>
+          <t>-3,22; 2,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 2,04</t>
+          <t>-3,47; 2,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 5,0</t>
+          <t>-0,3; 5,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 3,3</t>
+          <t>-3,64; 3,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2005-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 5,05</t>
+          <t>-8,95; 5,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 1,49</t>
+          <t>-6,04; 1,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,0</t>
+          <t>-3,55; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,92; 6,68</t>
+          <t>-16,88; 6,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 5,68</t>
+          <t>-9,5; 5,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 1,53</t>
+          <t>-6,14; 1,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,0</t>
+          <t>-3,55; 0,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 8,38</t>
+          <t>-19,17; 8,32</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 4,48</t>
+          <t>-3,36; 4,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 2,16</t>
+          <t>-5,92; 2,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 2,0</t>
+          <t>-4,86; 1,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 5,07</t>
+          <t>-6,67; 4,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 4,99</t>
+          <t>-3,59; 5,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 2,36</t>
+          <t>-6,28; 2,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 2,12</t>
+          <t>-5,02; 1,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 5,95</t>
+          <t>-7,25; 5,6</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 5,94</t>
+          <t>-8,9; 5,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 7,22</t>
+          <t>-5,21; 7,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 12,91</t>
+          <t>1,96; 12,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 8,36</t>
+          <t>-4,16; 8,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 7,35</t>
+          <t>-10,28; 7,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 8,63</t>
+          <t>-5,74; 8,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 16,1</t>
+          <t>2,26; 15,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 10,16</t>
+          <t>-4,69; 9,86</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 5,78</t>
+          <t>-4,65; 5,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 7,31</t>
+          <t>-5,46; 6,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 8,5</t>
+          <t>-3,06; 9,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 5,13</t>
+          <t>-5,2; 4,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 6,91</t>
+          <t>-5,21; 7,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 8,89</t>
+          <t>-6,18; 8,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 10,14</t>
+          <t>-3,49; 10,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 6,0</t>
+          <t>-5,72; 5,63</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 2,51</t>
+          <t>-2,66; 2,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,24</t>
+          <t>-3,37; 2,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,47</t>
+          <t>-0,34; 4,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 3,26</t>
+          <t>-3,24; 3,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 2,83</t>
+          <t>-2,95; 3,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 2,52</t>
+          <t>-3,65; 2,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 5,04</t>
+          <t>-0,37; 5,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 3,77</t>
+          <t>-3,68; 3,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2005-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-5,33</t>
+          <t>-5,25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-6,31%</t>
+          <t>-6,24%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 5,19</t>
+          <t>-8,75; 4,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 1,34</t>
+          <t>-5,03; 1,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,0</t>
+          <t>-3,71; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 6,69</t>
+          <t>-17,12; 7,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 5,77</t>
+          <t>-9,27; 5,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 1,34</t>
+          <t>-5,07; 1,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,0</t>
+          <t>-3,71; 0,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-19,17; 8,32</t>
+          <t>-19,16; 9,44</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,62</t>
+          <t>-1,03</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-0,71%</t>
+          <t>-1,17%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 4,82</t>
+          <t>-2,9; 4,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 2,08</t>
+          <t>-5,89; 2,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 1,84</t>
+          <t>-4,51; 2,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 4,75</t>
+          <t>-7,63; 4,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 5,39</t>
+          <t>-3,08; 5,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 2,23</t>
+          <t>-6,19; 2,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 1,95</t>
+          <t>-4,62; 2,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 5,6</t>
+          <t>-8,35; 5,14</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,79</t>
+          <t>1,53</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 5,94</t>
+          <t>-8,82; 5,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 7,07</t>
+          <t>-5,51; 6,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 12,8</t>
+          <t>2,02; 12,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 8,01</t>
+          <t>-5,18; 7,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 7,38</t>
+          <t>-10,19; 6,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 8,47</t>
+          <t>-6,05; 8,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 15,78</t>
+          <t>2,45; 16,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 9,86</t>
+          <t>-5,84; 9,14</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-0,34%</t>
+          <t>-1,33%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 5,9</t>
+          <t>-4,61; 6,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 6,66</t>
+          <t>-5,63; 6,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 9,09</t>
+          <t>-3,39; 8,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 4,84</t>
+          <t>-6,15; 3,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 7,06</t>
+          <t>-5,09; 7,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 8,01</t>
+          <t>-6,45; 7,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 10,93</t>
+          <t>-3,67; 10,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 5,63</t>
+          <t>-6,69; 3,91</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,74</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-0,2%</t>
+          <t>-0,84%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,69</t>
+          <t>-2,92; 2,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 2,0</t>
+          <t>-3,24; 1,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 4,7</t>
+          <t>-0,36; 4,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 3,13</t>
+          <t>-4,32; 2,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 3,09</t>
+          <t>-3,27; 3,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 2,23</t>
+          <t>-3,53; 2,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 5,25</t>
+          <t>-0,34; 5,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 3,65</t>
+          <t>-4,8; 2,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2005-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP2005-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,89</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,45</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,25</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,04%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-0,65%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-6,24%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.88906198078852</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.452999596131588</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.6493503039053383</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-5.254753142486191</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.02039352291114523</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.01472573518864346</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.006493503039053383</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.06244164674601665</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-8,75; 4,96</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,03; 1,34</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-3,71; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-17,12; 7,46</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-9,27; 5,55</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-5,07; 1,36</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-3,71; 0,0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-19,16; 9,44</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-8.753864719945051</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.031199684563676</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.707199763313664</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-17.11525243513143</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.09266161926135438</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.050654271611277</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.03707199763313664</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.1915875268953738</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4.957961770300912</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.342838140533998</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.463517303375757</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.05554397067053369</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.01360161391332692</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.0943612941086153</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,79</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,23</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,03</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-1,91%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-1,28%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-1,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,9; 4,57</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,89; 2,54</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,51; 2,04</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-7,63; 4,46</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-3,08; 5,11</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-6,19; 2,76</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-4,62; 2,16</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-8,35; 5,14</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.7025918299461753</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.789718857052591</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.232573459834707</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.029929555385833</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.007657327256280376</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.01908938918458532</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.01284722642149887</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.01170093227500843</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-1,2</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,69</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7,42</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,53</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,41%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.899351950143729</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.885312499343001</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.506167206497898</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-7.627891259817114</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.03084593068673823</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.06192865662984571</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.046234617780701</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.08350934493363608</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-8,82; 5,57</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,51; 6,72</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2,02; 12,9</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-5,18; 7,63</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-10,19; 6,76</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-6,05; 8,19</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2,45; 16,2</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-5,84; 9,14</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.571361335531727</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.537731782021706</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.0412913044757</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>4.456012736550323</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.05114220429561502</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.02760909525646913</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.02155390856522144</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.05140711964080363</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,49</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,45</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,19</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-1,33%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-1.195477014385982</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.6878622525610112</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>7.416748816434415</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.529748372238104</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.01412618764758555</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.007903500997480247</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.08744383859359509</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.01788194466055588</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,61; 6,43</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,63; 6,62</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,39; 8,46</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-6,15; 3,37</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-5,09; 7,73</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-6,45; 7,91</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-3,67; 10,24</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-6,69; 3,91</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-8.815515466750194</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.505104309111522</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>2.022281448093232</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.179472651170252</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.101922706646584</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.06054806523946746</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>0.02446642287632568</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.05836986510023853</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.567529477172424</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.724970190415671</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>12.89584470186398</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7.630799596212133</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.06764081169194516</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.0818737212996828</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.1619584699990917</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.09140128524875796</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.4882831410842892</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.6274866719658601</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.454817504759266</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.194784414077321</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.005646286172976711</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.007311451073300103</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.02824091743103939</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.01327240499083453</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.605687202352352</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.634676472342945</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.389823456663252</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-6.145028998732626</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.05090754872562678</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.06446060351635585</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.03665539604620614</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.06688055937154409</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.428578412106427</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6.618648596496866</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>8.463213619318603</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3.37019326202295</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.07733087282467235</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.07910162812921737</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.1023690487901523</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.039117773066901</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,57</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,74</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,63%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-0,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,92; 2,81</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,24; 1,82</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,36; 4,45</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-4,32; 2,22</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-3,27; 3,21</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-3,53; 2,04</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-0,34; 5,0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-4,8; 2,63</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.01641568973587137</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.572213631835139</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2.04432851766766</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.7412044644342974</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.0001848168092523929</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.006294542833068484</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.02241949120713237</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.008429588878299641</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.922927534006437</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.236555473797076</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.359802305542555</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-4.320230565958391</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.03272426545965557</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.03527398787287953</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.003430869012643234</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.04798518101580782</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.806071217579716</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.822270207537349</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.449262631310874</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.219703258389621</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.03212272690997615</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.0203661959940989</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.04995044099371614</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.02632751823094234</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
